--- a/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=80_without_41.xlsx
+++ b/result/LOOCV/SVR/without_41/nBA/1&2_nBA_SVR_LOOCV_mechanism_oriented_perc=80_without_41.xlsx
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7344674423458069</v>
+        <v>0.7344674423458073</v>
       </c>
       <c r="C3" t="n">
         <v>1.815729463123842</v>
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9281574052067806</v>
+        <v>0.9281574052067807</v>
       </c>
       <c r="C4" t="n">
-        <v>1.856479583260191</v>
+        <v>1.85647958326019</v>
       </c>
       <c r="D4" t="n">
         <v>2.05</v>
@@ -503,7 +503,7 @@
         <v>0.8860063906659643</v>
       </c>
       <c r="C5" t="n">
-        <v>2.116963701972287</v>
+        <v>2.116963701972282</v>
       </c>
       <c r="D5" t="n">
         <v>1.9</v>
@@ -516,10 +516,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7935696953450355</v>
+        <v>0.9301612847842105</v>
       </c>
       <c r="C6" t="n">
-        <v>1.950667995003196</v>
+        <v>2.032319400203713</v>
       </c>
       <c r="D6" t="n">
         <v>1.75</v>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.816588760242265</v>
+        <v>0.8165887602422632</v>
       </c>
       <c r="C7" t="n">
         <v>1.598676022617539</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7648303049619498</v>
+        <v>0.7648303049619503</v>
       </c>
       <c r="C12" t="n">
         <v>1.412151378141284</v>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7439922004779003</v>
+        <v>0.9205200529796188</v>
       </c>
       <c r="C13" t="n">
-        <v>1.53792708969103</v>
+        <v>1.499189239490605</v>
       </c>
       <c r="D13" t="n">
         <v>1.45</v>
@@ -676,7 +676,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8537687361736365</v>
+        <v>0.8537687361736362</v>
       </c>
       <c r="C16" t="n">
         <v>1.338219670154086</v>
@@ -708,10 +708,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7593151492380799</v>
+        <v>0.8117673423584586</v>
       </c>
       <c r="C18" t="n">
-        <v>2.783612351934546</v>
+        <v>2.846217142369086</v>
       </c>
       <c r="D18" t="n">
         <v>1.95</v>
